--- a/nhapcongviehangthang/nhapcv-thang4.xlsx
+++ b/nhapcongviehangthang/nhapcv-thang4.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A010E3FC-EC08-7E4A-B2F1-326CA2D6C125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE6E14F-FDC3-7D47-8764-D9B3758C92F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapLieu" sheetId="1" r:id="rId1"/>
-    <sheet name="DanhMuc" sheetId="2" r:id="rId2"/>
+    <sheet name="DanhMuc" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/nhapcongviehangthang/nhapcv-thang4.xlsx
+++ b/nhapcongviehangthang/nhapcv-thang4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE6E14F-FDC3-7D47-8764-D9B3758C92F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF236297-A76E-6C44-9921-D5841E46E10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,33 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
-    <t>Lĩnh vực lớn</t>
-  </si>
-  <si>
-    <t>Lĩnh vực con</t>
-  </si>
-  <si>
-    <t>Công việc</t>
-  </si>
-  <si>
-    <t>Sản phẩm</t>
-  </si>
-  <si>
-    <t>Ngày giao</t>
-  </si>
-  <si>
-    <t>Hạn</t>
-  </si>
-  <si>
-    <t>Ngày HT</t>
-  </si>
-  <si>
-    <t>Tham mưu</t>
-  </si>
-  <si>
-    <t>Phụ trách</t>
-  </si>
-  <si>
     <t>I. Văn phòng - Tuyên giáo - Xây dựng Đoàn</t>
   </si>
   <si>
@@ -108,6 +81,33 @@
   </si>
   <si>
     <t>Báo cáo Tháng Thanh niên</t>
+  </si>
+  <si>
+    <t>linh_vuc_lon</t>
+  </si>
+  <si>
+    <t>linh_vuc_con</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>san_pham</t>
+  </si>
+  <si>
+    <t>ngay_giao</t>
+  </si>
+  <si>
+    <t>han_hoan_thanh</t>
+  </si>
+  <si>
+    <t>ngay_hoan_thanh</t>
+  </si>
+  <si>
+    <t>can_bo_tham_muu</t>
+  </si>
+  <si>
+    <t>can_bo_phu_trach</t>
   </si>
 </sst>
 </file>
@@ -506,8 +506,8 @@
     <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.5" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="1"/>
@@ -515,42 +515,42 @@
   <sheetData>
     <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="7">
@@ -888,77 +888,77 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/nhapcongviehangthang/nhapcv-thang4.xlsx
+++ b/nhapcongviehangthang/nhapcv-thang4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF236297-A76E-6C44-9921-D5841E46E10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C2B311-9E8A-BC42-B550-478BADE096DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+  <si>
+    <t>Lĩnh vực lớn</t>
+  </si>
+  <si>
+    <t>Lĩnh vực con</t>
+  </si>
+  <si>
+    <t>Công việc</t>
+  </si>
+  <si>
+    <t>Sản phẩm</t>
+  </si>
+  <si>
+    <t>Ngày giao</t>
+  </si>
   <si>
     <t>I. Văn phòng - Tuyên giáo - Xây dựng Đoàn</t>
   </si>
@@ -83,31 +98,19 @@
     <t>Báo cáo Tháng Thanh niên</t>
   </si>
   <si>
-    <t>linh_vuc_lon</t>
-  </si>
-  <si>
-    <t>linh_vuc_con</t>
-  </si>
-  <si>
-    <t>ten</t>
-  </si>
-  <si>
-    <t>san_pham</t>
-  </si>
-  <si>
-    <t>ngay_giao</t>
-  </si>
-  <si>
-    <t>han_hoan_thanh</t>
-  </si>
-  <si>
-    <t>ngay_hoan_thanh</t>
-  </si>
-  <si>
-    <t>can_bo_tham_muu</t>
-  </si>
-  <si>
-    <t>can_bo_phu_trach</t>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Hạn hoàn thành</t>
+  </si>
+  <si>
+    <t>Ngày hoàn thành</t>
+  </si>
+  <si>
+    <t>Cán bộ tham mưu</t>
+  </si>
+  <si>
+    <t>Cán bộ phụ trách</t>
   </si>
 </sst>
 </file>
@@ -115,7 +118,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -188,14 +191,18 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,376 +505,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="7" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.5" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>23</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="6">
+        <v>46114</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46117</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="19" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7">
-        <v>46114</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46117</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" xr:uid="{D0963D4D-B397-D841-AF91-7518D5D3485A}">
+          <x14:formula1>
+            <xm:f>DanhMuc!$C$1:$C$30</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A300</xm:sqref>
+          <xm:sqref>A2:A293</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$B$1:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B300</xm:sqref>
+          <xm:sqref>B2:B293</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$C$1:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I300 H3:H300</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{D0963D4D-B397-D841-AF91-7518D5D3485A}">
-          <x14:formula1>
-            <xm:f>DanhMuc!$C$1:$C$30</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2</xm:sqref>
+          <xm:sqref>I2 H3:I293</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -888,77 +625,77 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
